--- a/Docs/Costs/Intake/INTAKE_COST_ESTIMATE.xlsx
+++ b/Docs/Costs/Intake/INTAKE_COST_ESTIMATE.xlsx
@@ -847,11 +847,11 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Worker requests per page load (gated HTML document)</t>
+          <t>Worker requests per page load (gated HTML document + identity list)</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>run_worker_first covers /, /index.html, /agent</t>
+          <t>run_worker_first covers /, /index.html, /agent; GET /demo/identities touches no D1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">

--- a/Docs/Costs/Intake/INTAKE_COST_ESTIMATE.xlsx
+++ b/Docs/Costs/Intake/INTAKE_COST_ESTIMATE.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -118,6 +118,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2233,7 +2234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2249,8 @@
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2312,7 +2315,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Within Free (&lt;= trigger)?</t>
+          <t>Within daily Free limits?</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -2323,6 +2326,16 @@
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Peak D1 writes/s</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Upgrade policy (&gt; trigger)?</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Share of 500 MB by 2026-10-31 (2,000-char cases)</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2378,7 @@
         <v/>
       </c>
       <c r="J5" s="2">
-        <f>IF(I5&lt;=Inputs!$B$29,"yes","no: upgrade")</f>
+        <f>IF(I5&lt;=1,"yes","no: exceeds Free")</f>
         <v/>
       </c>
       <c r="K5" s="8">
@@ -2376,6 +2389,14 @@
         <f>G5/86400*Inputs!$B$10</f>
         <v/>
       </c>
+      <c r="M5" s="2">
+        <f>IF(I5&gt;Inputs!$B$29,"yes: move to Paid","no")</f>
+        <v/>
+      </c>
+      <c r="N5" s="7">
+        <f>B5*Inputs!$B$8*Inputs!$B$21/(Inputs!$B$27*1000000)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2416,7 +2437,7 @@
         <v/>
       </c>
       <c r="J6" s="2">
-        <f>IF(I6&lt;=Inputs!$B$29,"yes","no: upgrade")</f>
+        <f>IF(I6&lt;=1,"yes","no: exceeds Free")</f>
         <v/>
       </c>
       <c r="K6" s="8">
@@ -2427,6 +2448,14 @@
         <f>G6/86400*Inputs!$B$10</f>
         <v/>
       </c>
+      <c r="M6" s="2">
+        <f>IF(I6&gt;Inputs!$B$29,"yes: move to Paid","no")</f>
+        <v/>
+      </c>
+      <c r="N6" s="7">
+        <f>B6*Inputs!$B$8*Inputs!$B$21/(Inputs!$B$27*1000000)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2467,7 +2496,7 @@
         <v/>
       </c>
       <c r="J7" s="2">
-        <f>IF(I7&lt;=Inputs!$B$29,"yes","no: upgrade")</f>
+        <f>IF(I7&lt;=1,"yes","no: exceeds Free")</f>
         <v/>
       </c>
       <c r="K7" s="8">
@@ -2478,6 +2507,14 @@
         <f>G7/86400*Inputs!$B$10</f>
         <v/>
       </c>
+      <c r="M7" s="2">
+        <f>IF(I7&gt;Inputs!$B$29,"yes: move to Paid","no")</f>
+        <v/>
+      </c>
+      <c r="N7" s="7">
+        <f>B7*Inputs!$B$8*Inputs!$B$21/(Inputs!$B$27*1000000)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2518,7 +2555,7 @@
         <v/>
       </c>
       <c r="J8" s="2">
-        <f>IF(I8&lt;=Inputs!$B$29,"yes","no: upgrade")</f>
+        <f>IF(I8&lt;=1,"yes","no: exceeds Free")</f>
         <v/>
       </c>
       <c r="K8" s="8">
@@ -2529,16 +2566,53 @@
         <f>G8/86400*Inputs!$B$10</f>
         <v/>
       </c>
+      <c r="M8" s="2">
+        <f>IF(I8&gt;Inputs!$B$29,"yes: move to Paid","no")</f>
+        <v/>
+      </c>
+      <c r="N8" s="7">
+        <f>B8*Inputs!$B$8*Inputs!$B$21/(Inputs!$B$27*1000000)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Free capacity (episodes/day)</t>
+          <t>Daily-quota bound (episodes/day)</t>
         </is>
       </c>
       <c r="B10" s="11">
         <f>MIN(Inputs!$B$23/(Inputs!$B$11+Inputs!$B$12+Inputs!$B$17*Inputs!$B$16),Inputs!$B$25/(Inputs!$B$14+Inputs!$B$18*Inputs!$B$16),Inputs!$B$26/(Inputs!$B$15+Inputs!$B$19*Inputs!$B$16))</f>
         <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Days until 500 MB at that rate (typical case)</t>
+        </is>
+      </c>
+      <c r="B11" s="11">
+        <f>Inputs!$B$27*1000000/(B10*Inputs!$B$20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Days until 500 MB at that rate (2,000-char cases)</t>
+        </is>
+      </c>
+      <c r="B12" s="12">
+        <f>Inputs!$B$27*1000000/(B10*Inputs!$B$21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>The daily-quota bound is not a whole-window capacity: storage is cumulative and can bind first.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2603,7 +2677,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>AWS O4: Lambda + RDS + NAT (indicative)</t>
+          <t>AWS O4: API + Lambda + RDS + NAT, no DynamoDB (indicative)</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -2618,26 +2692,25 @@
           <t>S1</t>
         </is>
       </c>
-      <c r="B5" s="12">
-        <f>IF('Cloudflare capacity'!I5&lt;=Inputs!$B$29,0,"exceeds Free")</f>
-        <v/>
-      </c>
-      <c r="C5" s="12">
+      <c r="B5" s="13">
+        <f>IF('Cloudflare capacity'!I5&lt;=1,0,"exceeds Free")</f>
+        <v/>
+      </c>
+      <c r="C5" s="13">
         <f>Inputs!$B$30+MAX(0,'Cloudflare capacity'!C5*Inputs!$B$9-Inputs!$B$31)*Inputs!$B$32/1000000+MAX(0,'Cloudflare capacity'!C5*Inputs!$B$9*Inputs!$B$22-Inputs!$B$33)*Inputs!$B$34/1000000+MAX(0,'Cloudflare capacity'!E5*Inputs!$B$9-Inputs!$B$35)*Inputs!$B$36/1000000+MAX(0,'Cloudflare capacity'!G5*Inputs!$B$9-Inputs!$B$37)*Inputs!$B$38/1000000</f>
         <v/>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="13">
         <f>MAX(0,(Inputs!$B$4*(Inputs!$B$12+Inputs!$B$17*Inputs!$B$16)*Inputs!$B$9)-Inputs!$B$41)*Inputs!$B$39/1000000+MAX(0,(Inputs!$B$4*(Inputs!$B$12+Inputs!$B$17*Inputs!$B$16)*Inputs!$B$9)*Inputs!$B$43*Inputs!$B$44-Inputs!$B$42)*Inputs!$B$40+(Inputs!$B$4*(Inputs!$B$12+Inputs!$B$17*Inputs!$B$16)*Inputs!$B$9)*Inputs!$B$45/1000000+'Cloudflare capacity'!G5*Inputs!$B$9*Inputs!$B$46/1000000+'Cloudflare capacity'!E5*Inputs!$B$9*Inputs!$B$48*Inputs!$B$47/1000000</f>
         <v/>
       </c>
-      <c r="E5" s="12">
-        <f>D5+Inputs!$B$51+Inputs!$B$52+(Inputs!$B$49+Inputs!$B$50)*Inputs!$B$53</f>
-        <v/>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>RDS rows are indicative; confirm in the AWS Pricing Calculator</t>
-        </is>
+      <c r="E5" s="13">
+        <f>MAX(0,(Inputs!$B$4*(Inputs!$B$12+Inputs!$B$17*Inputs!$B$16)*Inputs!$B$9)-Inputs!$B$41)*Inputs!$B$39/1000000+MAX(0,(Inputs!$B$4*(Inputs!$B$12+Inputs!$B$17*Inputs!$B$16)*Inputs!$B$9)*Inputs!$B$43*Inputs!$B$44-Inputs!$B$42)*Inputs!$B$40+(Inputs!$B$4*(Inputs!$B$12+Inputs!$B$17*Inputs!$B$16)*Inputs!$B$9)*Inputs!$B$45/1000000+Inputs!$B$51+Inputs!$B$52+(Inputs!$B$49+Inputs!$B$50)*Inputs!$B$53</f>
+        <v/>
+      </c>
+      <c r="F5" s="2">
+        <f>IF('Cloudflare capacity'!I5&gt;Inputs!$B$29,"Within Free, but the upgrade policy calls for Workers Paid. ","")&amp;"O4 uses RDS instead of DynamoDB; RDS rows are indicative (AWS Pricing Calculator)."</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -2646,26 +2719,25 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="B6" s="12">
-        <f>IF('Cloudflare capacity'!I6&lt;=Inputs!$B$29,0,"exceeds Free")</f>
-        <v/>
-      </c>
-      <c r="C6" s="12">
+      <c r="B6" s="13">
+        <f>IF('Cloudflare capacity'!I6&lt;=1,0,"exceeds Free")</f>
+        <v/>
+      </c>
+      <c r="C6" s="13">
         <f>Inputs!$B$30+MAX(0,'Cloudflare capacity'!C6*Inputs!$B$9-Inputs!$B$31)*Inputs!$B$32/1000000+MAX(0,'Cloudflare capacity'!C6*Inputs!$B$9*Inputs!$B$22-Inputs!$B$33)*Inputs!$B$34/1000000+MAX(0,'Cloudflare capacity'!E6*Inputs!$B$9-Inputs!$B$35)*Inputs!$B$36/1000000+MAX(0,'Cloudflare capacity'!G6*Inputs!$B$9-Inputs!$B$37)*Inputs!$B$38/1000000</f>
         <v/>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="13">
         <f>MAX(0,(Inputs!$B$5*(Inputs!$B$12+Inputs!$B$17*Inputs!$B$16)*Inputs!$B$9)-Inputs!$B$41)*Inputs!$B$39/1000000+MAX(0,(Inputs!$B$5*(Inputs!$B$12+Inputs!$B$17*Inputs!$B$16)*Inputs!$B$9)*Inputs!$B$43*Inputs!$B$44-Inputs!$B$42)*Inputs!$B$40+(Inputs!$B$5*(Inputs!$B$12+Inputs!$B$17*Inputs!$B$16)*Inputs!$B$9)*Inputs!$B$45/1000000+'Cloudflare capacity'!G6*Inputs!$B$9*Inputs!$B$46/1000000+'Cloudflare capacity'!E6*Inputs!$B$9*Inputs!$B$48*Inputs!$B$47/1000000</f>
         <v/>
       </c>
-      <c r="E6" s="12">
-        <f>D6+Inputs!$B$51+Inputs!$B$52+(Inputs!$B$49+Inputs!$B$50)*Inputs!$B$53</f>
-        <v/>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>RDS rows are indicative; confirm in the AWS Pricing Calculator</t>
-        </is>
+      <c r="E6" s="13">
+        <f>MAX(0,(Inputs!$B$5*(Inputs!$B$12+Inputs!$B$17*Inputs!$B$16)*Inputs!$B$9)-Inputs!$B$41)*Inputs!$B$39/1000000+MAX(0,(Inputs!$B$5*(Inputs!$B$12+Inputs!$B$17*Inputs!$B$16)*Inputs!$B$9)*Inputs!$B$43*Inputs!$B$44-Inputs!$B$42)*Inputs!$B$40+(Inputs!$B$5*(Inputs!$B$12+Inputs!$B$17*Inputs!$B$16)*Inputs!$B$9)*Inputs!$B$45/1000000+Inputs!$B$51+Inputs!$B$52+(Inputs!$B$49+Inputs!$B$50)*Inputs!$B$53</f>
+        <v/>
+      </c>
+      <c r="F6" s="2">
+        <f>IF('Cloudflare capacity'!I6&gt;Inputs!$B$29,"Within Free, but the upgrade policy calls for Workers Paid. ","")&amp;"O4 uses RDS instead of DynamoDB; RDS rows are indicative (AWS Pricing Calculator)."</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -2674,26 +2746,25 @@
           <t>S3</t>
         </is>
       </c>
-      <c r="B7" s="12">
-        <f>IF('Cloudflare capacity'!I7&lt;=Inputs!$B$29,0,"exceeds Free")</f>
-        <v/>
-      </c>
-      <c r="C7" s="12">
+      <c r="B7" s="13">
+        <f>IF('Cloudflare capacity'!I7&lt;=1,0,"exceeds Free")</f>
+        <v/>
+      </c>
+      <c r="C7" s="13">
         <f>Inputs!$B$30+MAX(0,'Cloudflare capacity'!C7*Inputs!$B$9-Inputs!$B$31)*Inputs!$B$32/1000000+MAX(0,'Cloudflare capacity'!C7*Inputs!$B$9*Inputs!$B$22-Inputs!$B$33)*Inputs!$B$34/1000000+MAX(0,'Cloudflare capacity'!E7*Inputs!$B$9-Inputs!$B$35)*Inputs!$B$36/1000000+MAX(0,'Cloudflare capacity'!G7*Inputs!$B$9-Inputs!$B$37)*Inputs!$B$38/1000000</f>
         <v/>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="13">
         <f>MAX(0,(Inputs!$B$6*(Inputs!$B$12+Inputs!$B$17*Inputs!$B$16)*Inputs!$B$9)-Inputs!$B$41)*Inputs!$B$39/1000000+MAX(0,(Inputs!$B$6*(Inputs!$B$12+Inputs!$B$17*Inputs!$B$16)*Inputs!$B$9)*Inputs!$B$43*Inputs!$B$44-Inputs!$B$42)*Inputs!$B$40+(Inputs!$B$6*(Inputs!$B$12+Inputs!$B$17*Inputs!$B$16)*Inputs!$B$9)*Inputs!$B$45/1000000+'Cloudflare capacity'!G7*Inputs!$B$9*Inputs!$B$46/1000000+'Cloudflare capacity'!E7*Inputs!$B$9*Inputs!$B$48*Inputs!$B$47/1000000</f>
         <v/>
       </c>
-      <c r="E7" s="12">
-        <f>D7+Inputs!$B$51+Inputs!$B$52+(Inputs!$B$49+Inputs!$B$50)*Inputs!$B$53</f>
-        <v/>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>RDS rows are indicative; confirm in the AWS Pricing Calculator</t>
-        </is>
+      <c r="E7" s="13">
+        <f>MAX(0,(Inputs!$B$6*(Inputs!$B$12+Inputs!$B$17*Inputs!$B$16)*Inputs!$B$9)-Inputs!$B$41)*Inputs!$B$39/1000000+MAX(0,(Inputs!$B$6*(Inputs!$B$12+Inputs!$B$17*Inputs!$B$16)*Inputs!$B$9)*Inputs!$B$43*Inputs!$B$44-Inputs!$B$42)*Inputs!$B$40+(Inputs!$B$6*(Inputs!$B$12+Inputs!$B$17*Inputs!$B$16)*Inputs!$B$9)*Inputs!$B$45/1000000+Inputs!$B$51+Inputs!$B$52+(Inputs!$B$49+Inputs!$B$50)*Inputs!$B$53</f>
+        <v/>
+      </c>
+      <c r="F7" s="2">
+        <f>IF('Cloudflare capacity'!I7&gt;Inputs!$B$29,"Within Free, but the upgrade policy calls for Workers Paid. ","")&amp;"O4 uses RDS instead of DynamoDB; RDS rows are indicative (AWS Pricing Calculator)."</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -2702,26 +2773,25 @@
           <t>S4</t>
         </is>
       </c>
-      <c r="B8" s="12">
-        <f>IF('Cloudflare capacity'!I8&lt;=Inputs!$B$29,0,"exceeds Free")</f>
-        <v/>
-      </c>
-      <c r="C8" s="12">
+      <c r="B8" s="13">
+        <f>IF('Cloudflare capacity'!I8&lt;=1,0,"exceeds Free")</f>
+        <v/>
+      </c>
+      <c r="C8" s="13">
         <f>Inputs!$B$30+MAX(0,'Cloudflare capacity'!C8*Inputs!$B$9-Inputs!$B$31)*Inputs!$B$32/1000000+MAX(0,'Cloudflare capacity'!C8*Inputs!$B$9*Inputs!$B$22-Inputs!$B$33)*Inputs!$B$34/1000000+MAX(0,'Cloudflare capacity'!E8*Inputs!$B$9-Inputs!$B$35)*Inputs!$B$36/1000000+MAX(0,'Cloudflare capacity'!G8*Inputs!$B$9-Inputs!$B$37)*Inputs!$B$38/1000000</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="13">
         <f>MAX(0,(Inputs!$B$7*(Inputs!$B$12+Inputs!$B$17*Inputs!$B$16)*Inputs!$B$9)-Inputs!$B$41)*Inputs!$B$39/1000000+MAX(0,(Inputs!$B$7*(Inputs!$B$12+Inputs!$B$17*Inputs!$B$16)*Inputs!$B$9)*Inputs!$B$43*Inputs!$B$44-Inputs!$B$42)*Inputs!$B$40+(Inputs!$B$7*(Inputs!$B$12+Inputs!$B$17*Inputs!$B$16)*Inputs!$B$9)*Inputs!$B$45/1000000+'Cloudflare capacity'!G8*Inputs!$B$9*Inputs!$B$46/1000000+'Cloudflare capacity'!E8*Inputs!$B$9*Inputs!$B$48*Inputs!$B$47/1000000</f>
         <v/>
       </c>
-      <c r="E8" s="12">
-        <f>D8+Inputs!$B$51+Inputs!$B$52+(Inputs!$B$49+Inputs!$B$50)*Inputs!$B$53</f>
-        <v/>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>RDS rows are indicative; confirm in the AWS Pricing Calculator</t>
-        </is>
+      <c r="E8" s="13">
+        <f>MAX(0,(Inputs!$B$7*(Inputs!$B$12+Inputs!$B$17*Inputs!$B$16)*Inputs!$B$9)-Inputs!$B$41)*Inputs!$B$39/1000000+MAX(0,(Inputs!$B$7*(Inputs!$B$12+Inputs!$B$17*Inputs!$B$16)*Inputs!$B$9)*Inputs!$B$43*Inputs!$B$44-Inputs!$B$42)*Inputs!$B$40+(Inputs!$B$7*(Inputs!$B$12+Inputs!$B$17*Inputs!$B$16)*Inputs!$B$9)*Inputs!$B$45/1000000+Inputs!$B$51+Inputs!$B$52+(Inputs!$B$49+Inputs!$B$50)*Inputs!$B$53</f>
+        <v/>
+      </c>
+      <c r="F8" s="2">
+        <f>IF('Cloudflare capacity'!I8&gt;Inputs!$B$29,"Within Free, but the upgrade policy calls for Workers Paid. ","")&amp;"O4 uses RDS instead of DynamoDB; RDS rows are indicative (AWS Pricing Calculator)."</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2800,7 +2870,7 @@
           <t>Workers AI gpt-oss-20b</t>
         </is>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="14">
         <f>((Inputs!$B$54*Inputs!$B$58+Inputs!$B$55*Inputs!$B$59)/1000000)*Inputs!$B$57/1000</f>
         <v/>
       </c>
@@ -2808,19 +2878,19 @@
         <f>Inputs!$B$56/((Inputs!$B$54*Inputs!$B$58+Inputs!$B$55*Inputs!$B$59)/1000000)</f>
         <v/>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="13">
         <f>((Inputs!$B$54*Inputs!$B$58+Inputs!$B$55*Inputs!$B$59)/1000000)*Inputs!$B$57/1000*Inputs!$B$4*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="13">
         <f>((Inputs!$B$54*Inputs!$B$58+Inputs!$B$55*Inputs!$B$59)/1000000)*Inputs!$B$57/1000*Inputs!$B$5*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="13">
         <f>((Inputs!$B$54*Inputs!$B$58+Inputs!$B$55*Inputs!$B$59)/1000000)*Inputs!$B$57/1000*Inputs!$B$6*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="13">
         <f>((Inputs!$B$54*Inputs!$B$58+Inputs!$B$55*Inputs!$B$59)/1000000)*Inputs!$B$57/1000*Inputs!$B$7*Inputs!$B$9</f>
         <v/>
       </c>
@@ -2831,7 +2901,7 @@
           <t>Workers AI llama-3.3-70b</t>
         </is>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="14">
         <f>((Inputs!$B$54*Inputs!$B$60+Inputs!$B$55*Inputs!$B$61)/1000000)*Inputs!$B$57/1000</f>
         <v/>
       </c>
@@ -2839,19 +2909,19 @@
         <f>Inputs!$B$56/((Inputs!$B$54*Inputs!$B$60+Inputs!$B$55*Inputs!$B$61)/1000000)</f>
         <v/>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="13">
         <f>((Inputs!$B$54*Inputs!$B$60+Inputs!$B$55*Inputs!$B$61)/1000000)*Inputs!$B$57/1000*Inputs!$B$4*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="13">
         <f>((Inputs!$B$54*Inputs!$B$60+Inputs!$B$55*Inputs!$B$61)/1000000)*Inputs!$B$57/1000*Inputs!$B$5*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="13">
         <f>((Inputs!$B$54*Inputs!$B$60+Inputs!$B$55*Inputs!$B$61)/1000000)*Inputs!$B$57/1000*Inputs!$B$6*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="13">
         <f>((Inputs!$B$54*Inputs!$B$60+Inputs!$B$55*Inputs!$B$61)/1000000)*Inputs!$B$57/1000*Inputs!$B$7*Inputs!$B$9</f>
         <v/>
       </c>
@@ -2862,7 +2932,7 @@
           <t>Claude Haiku 4.5</t>
         </is>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="14">
         <f>((Inputs!$B$54*Inputs!$B$62+Inputs!$B$55*Inputs!$B$63)/1000000)</f>
         <v/>
       </c>
@@ -2871,19 +2941,19 @@
           <t>none</t>
         </is>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="13">
         <f>((Inputs!$B$54*Inputs!$B$62+Inputs!$B$55*Inputs!$B$63)/1000000)*Inputs!$B$4*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="13">
         <f>((Inputs!$B$54*Inputs!$B$62+Inputs!$B$55*Inputs!$B$63)/1000000)*Inputs!$B$5*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="13">
         <f>((Inputs!$B$54*Inputs!$B$62+Inputs!$B$55*Inputs!$B$63)/1000000)*Inputs!$B$6*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="13">
         <f>((Inputs!$B$54*Inputs!$B$62+Inputs!$B$55*Inputs!$B$63)/1000000)*Inputs!$B$7*Inputs!$B$9</f>
         <v/>
       </c>
@@ -2894,7 +2964,7 @@
           <t>Claude Sonnet 5</t>
         </is>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="14">
         <f>((Inputs!$B$54*Inputs!$B$64+Inputs!$B$55*Inputs!$B$65)/1000000)</f>
         <v/>
       </c>
@@ -2903,19 +2973,19 @@
           <t>none</t>
         </is>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="13">
         <f>((Inputs!$B$54*Inputs!$B$64+Inputs!$B$55*Inputs!$B$65)/1000000)*Inputs!$B$4*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <f>((Inputs!$B$54*Inputs!$B$64+Inputs!$B$55*Inputs!$B$65)/1000000)*Inputs!$B$5*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <f>((Inputs!$B$54*Inputs!$B$64+Inputs!$B$55*Inputs!$B$65)/1000000)*Inputs!$B$6*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="13">
         <f>((Inputs!$B$54*Inputs!$B$64+Inputs!$B$55*Inputs!$B$65)/1000000)*Inputs!$B$7*Inputs!$B$9</f>
         <v/>
       </c>

--- a/Docs/Costs/Intake/INTAKE_COST_ESTIMATE.xlsx
+++ b/Docs/Costs/Intake/INTAKE_COST_ESTIMATE.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>D1 queries, rows and stored bytes come from local tests (back-end/test/integration/budget.test.js; SQLite with the Worker migrations). Worker CPU is not measured yet.</t>
+          <t>D1 queries, rows and stored bytes come from local tests (back-end/test/integration/budget.test.js; SQLite with the Worker migrations). Worker CPU was observed once in production (one episode, 0-4 ms per request, against the 10 ms Free limit). That was not a load test, so the model keeps 5 ms as a conservative planning value.</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Worker CPU per request</t>
+          <t>Worker CPU per request (planning value)</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Not measured; read the real value from Workers analytics after deploy</t>
+          <t>Conservative planning assumption. One production episode on 2026-09-29 (Workers Logs, 13 invocations) showed 0-4 ms per request; that is a single sample, not a load test. Free limit: 10 ms</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>assumption</t>
+          <t>assumption; single-episode observation 0-4 ms</t>
         </is>
       </c>
     </row>

--- a/Docs/Costs/Intake/INTAKE_COST_ESTIMATE.xlsx
+++ b/Docs/Costs/Intake/INTAKE_COST_ESTIMATE.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Run the intake service on Cloudflare Workers + D1 Free through 2026-10-31. Move to Workers Paid ($5/month) if any daily Free limit stays above 70% for 3 days.</t>
+          <t>Run the intake service on Cloudflare Workers + D1 Free through 2026-10-20. Move to Workers Paid ($5/month) if any daily Free limit stays above 70% for 3 days. This workbook models the legacy /cases flow; the guided flow's capacity (about 2,380 episodes a day) is in ADR-004 section 2.</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 to 2026-10-31. Finalists are announced on 2026-10-15.</t>
+          <t>2026-09-29 to 2026-10-20. Finalists are announced on 2026-10-15; everything online is shut down after 2026-10-20.</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 to 2026-10-31</t>
+          <t>2026-09-29 to 2026-10-20 (shutdown after 2026-10-20, ADR-004)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Cases stored by 2026-10-31 (MB, typical)</t>
+          <t>Cases stored by 2026-10-20 (MB, typical)</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>Share of 500 MB by 2026-10-31 (2,000-char cases)</t>
+          <t>Share of 500 MB by 2026-10-20 (2,000-char cases)</t>
         </is>
       </c>
     </row>
